--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/myominnoo/Documents/GitHub/cv/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774DB14F-0EE2-514F-9E1B-A000332BD32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AACC10-A828-A94F-A7CA-F31515295CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="500" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20260" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="384">
   <si>
     <t>Prince of Songkla University</t>
   </si>
@@ -1048,9 +1048,6 @@
     <t>Generated over 25 research outputs and publications in peer-reviewed international journals.</t>
   </si>
   <si>
-    <t>Served as an editor for three manuscript submissions, overseeing the peer review process, making editorial decisions, and ensuring that the submissions met the standards of the journal.</t>
-  </si>
-  <si>
     <t>Produced a technical report and policy document to inform the Thai government on healthcare access issues for marginalized populations, and organized a dissemination meeting with local, regional, and international stakeholders to share our findings and recommendations.</t>
   </si>
   <si>
@@ -1190,6 +1187,9 @@
   </si>
   <si>
     <t>Delving into the field of indigenous health and health economics in Canada</t>
+  </si>
+  <si>
+    <t>Serving as an academic editor, overseeing the peer review process, making editorial decisions, and ensuring that the submissions met the standards of the journal.</t>
   </si>
 </sst>
 </file>
@@ -2566,7 +2566,7 @@
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2648,18 +2648,18 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -2670,79 +2670,79 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3136,16 +3136,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D2" t="s">
         <v>370</v>
-      </c>
-      <c r="D2" t="s">
-        <v>371</v>
       </c>
       <c r="E2" t="s">
         <v>181</v>
@@ -3646,13 +3646,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -3660,27 +3660,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
         <v>0</v>
@@ -3688,13 +3688,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D5" t="s">
         <v>0</v>
@@ -3702,13 +3702,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -3716,16 +3716,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D7" t="s">
         <v>366</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C7" t="s">
-        <v>360</v>
-      </c>
-      <c r="D7" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -3806,31 +3806,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" t="s">
         <v>379</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>380</v>
-      </c>
-      <c r="C2" t="s">
-        <v>381</v>
       </c>
       <c r="D2">
         <v>2023</v>
       </c>
-      <c r="E2" t="s">
-        <v>111</v>
-      </c>
       <c r="F2" t="s">
         <v>111</v>
       </c>
       <c r="G2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2" t="s">
         <v>54</v>
       </c>
       <c r="I2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -3838,7 +3835,7 @@
         <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C3" t="s">
         <v>110</v>
@@ -3847,7 +3844,7 @@
         <v>2022</v>
       </c>
       <c r="E3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F3">
         <v>2023</v>
@@ -3859,7 +3856,7 @@
         <v>54</v>
       </c>
       <c r="I3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -3867,7 +3864,7 @@
         <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
@@ -3876,7 +3873,7 @@
         <v>2022</v>
       </c>
       <c r="E4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F4">
         <v>2023</v>
@@ -3888,7 +3885,7 @@
         <v>54</v>
       </c>
       <c r="I4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -3896,7 +3893,7 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C5" t="s">
         <v>110</v>
@@ -3905,7 +3902,7 @@
         <v>2022</v>
       </c>
       <c r="E5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F5">
         <v>2023</v>
@@ -3925,7 +3922,7 @@
         <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C6" t="s">
         <v>110</v>
@@ -3934,7 +3931,7 @@
         <v>2022</v>
       </c>
       <c r="E6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F6">
         <v>2023</v>
@@ -3954,7 +3951,7 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
@@ -3963,7 +3960,7 @@
         <v>2022</v>
       </c>
       <c r="E7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F7">
         <v>2023</v>
@@ -3975,7 +3972,7 @@
         <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -3983,7 +3980,7 @@
         <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
@@ -3998,7 +3995,7 @@
         <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>336</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -4288,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -4656,7 +4653,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -4768,7 +4765,7 @@
         <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
